--- a/Rega_Local_Idcontador_origem_ZMC.xlsx
+++ b/Rega_Local_Idcontador_origem_ZMC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\regin\Desktop\ShareFiles\QGIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6F974CC-CE43-4F4A-8809-C5A03677A9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{A7DFA8C8-2FDD-4D9A-A6D6-87B16983D054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10272"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="473">
   <si>
     <t>IDLocaliza</t>
   </si>
@@ -1433,13 +1433,22 @@
   </si>
   <si>
     <t>Triângulo VG AdA</t>
+  </si>
+  <si>
+    <t>Furo</t>
+  </si>
+  <si>
+    <t>BOMBAGEM_DD</t>
+  </si>
+  <si>
+    <t>PE Dunas Douradas Furo 2 e 4 DD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1570,6 +1579,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1922,10 +1937,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Cor1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2329,7 +2345,7 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>470</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
@@ -2524,7 +2540,7 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>470</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
@@ -2556,27 +2572,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="1" t="str">
-        <f>A13</f>
-        <v>PRDD007</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="B13" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>20</v>
       </c>
     </row>

--- a/Rega_Local_Idcontador_origem_ZMC.xlsx
+++ b/Rega_Local_Idcontador_origem_ZMC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\regin\Desktop\ShareFiles\QGIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{A7DFA8C8-2FDD-4D9A-A6D6-87B16983D054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{E66011A2-496E-4671-B95E-08BE99B6E3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10272"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="474">
   <si>
     <t>IDLocaliza</t>
   </si>
@@ -1436,6 +1436,9 @@
   </si>
   <si>
     <t>Furo</t>
+  </si>
+  <si>
+    <t>Ada</t>
   </si>
   <si>
     <t>BOMBAGEM_DD</t>
@@ -2297,6 +2300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G235"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2331,7 +2335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2351,7 +2355,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2371,7 +2375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2391,7 +2395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2411,7 +2415,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -2434,7 +2438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -2457,7 +2461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2480,7 +2484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2503,7 +2507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2540,7 +2544,7 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
@@ -2549,7 +2553,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -2572,12 +2576,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>12</v>
@@ -2589,13 +2593,13 @@
         <v>470</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2618,7 +2622,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2641,7 +2645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2664,7 +2668,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -2687,7 +2691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -2710,7 +2714,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -2733,7 +2737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -2756,7 +2760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -2779,7 +2783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -2802,7 +2806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -2825,7 +2829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -2848,7 +2852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -2871,7 +2875,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2894,7 +2898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
@@ -2918,7 +2922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>64</v>
       </c>
@@ -2942,7 +2946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -2965,7 +2969,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -2988,7 +2992,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -3011,7 +3015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -3034,7 +3038,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -3057,7 +3061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -3080,7 +3084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -3103,7 +3107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -3126,7 +3130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -3149,7 +3153,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -3172,7 +3176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -3195,7 +3199,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -3218,7 +3222,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>90</v>
       </c>
@@ -3241,7 +3245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>92</v>
       </c>
@@ -3264,7 +3268,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -3287,7 +3291,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -3310,7 +3314,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -3333,7 +3337,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
         <v>100</v>
       </c>
@@ -3357,7 +3361,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>101</v>
       </c>
@@ -3380,7 +3384,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -3403,7 +3407,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
         <v>105</v>
       </c>
@@ -3427,7 +3431,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -3450,7 +3454,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
         <v>108</v>
       </c>
@@ -3474,7 +3478,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>109</v>
       </c>
@@ -3497,7 +3501,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>111</v>
       </c>
@@ -3520,7 +3524,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>113</v>
       </c>
@@ -3543,7 +3547,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
         <v>115</v>
       </c>
@@ -3567,7 +3571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>116</v>
       </c>
@@ -3591,7 +3595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>117</v>
       </c>
@@ -3615,7 +3619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
         <v>118</v>
       </c>
@@ -3639,7 +3643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>119</v>
       </c>
@@ -3662,7 +3666,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>122</v>
       </c>
@@ -3686,7 +3690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>123</v>
       </c>
@@ -3709,7 +3713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>125</v>
       </c>
@@ -3732,7 +3736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>127</v>
       </c>
@@ -3755,7 +3759,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -3778,7 +3782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>131</v>
       </c>
@@ -3801,7 +3805,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>133</v>
       </c>
@@ -3824,7 +3828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>135</v>
       </c>
@@ -3847,7 +3851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>137</v>
       </c>
@@ -3870,7 +3874,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>139</v>
       </c>
@@ -3893,7 +3897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>141</v>
       </c>
@@ -3916,7 +3920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>143</v>
       </c>
@@ -3939,7 +3943,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>145</v>
       </c>
@@ -3962,7 +3966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>147</v>
       </c>
@@ -3985,7 +3989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>149</v>
       </c>
@@ -4008,7 +4012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>151</v>
       </c>
@@ -4031,7 +4035,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="2" t="s">
         <v>153</v>
       </c>
@@ -4054,7 +4058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="2" t="s">
         <v>155</v>
       </c>
@@ -4077,7 +4081,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="2" t="s">
         <v>157</v>
       </c>
@@ -4100,7 +4104,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="2" t="s">
         <v>159</v>
       </c>
@@ -4123,7 +4127,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="2" t="s">
         <v>161</v>
       </c>
@@ -4146,7 +4150,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="2" t="s">
         <v>163</v>
       </c>
@@ -4169,7 +4173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="2" t="s">
         <v>165</v>
       </c>
@@ -4192,7 +4196,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="2" t="s">
         <v>167</v>
       </c>
@@ -4215,7 +4219,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="2" t="s">
         <v>169</v>
       </c>
@@ -4238,7 +4242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="2" t="s">
         <v>171</v>
       </c>
@@ -4261,7 +4265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="2" t="s">
         <v>173</v>
       </c>
@@ -4284,7 +4288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="2" t="s">
         <v>175</v>
       </c>
@@ -4307,7 +4311,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="2" t="s">
         <v>177</v>
       </c>
@@ -4330,7 +4334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="2" t="s">
         <v>179</v>
       </c>
@@ -4353,7 +4357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="2" t="s">
         <v>181</v>
       </c>
@@ -4376,7 +4380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="2" t="s">
         <v>183</v>
       </c>
@@ -4399,7 +4403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="2" t="s">
         <v>185</v>
       </c>
@@ -4422,7 +4426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="2" t="s">
         <v>187</v>
       </c>
@@ -4445,7 +4449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="2" t="s">
         <v>189</v>
       </c>
@@ -4468,7 +4472,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>191</v>
       </c>
@@ -4491,7 +4495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>193</v>
       </c>
@@ -4514,7 +4518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>195</v>
       </c>
@@ -4537,7 +4541,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>197</v>
       </c>
@@ -4560,7 +4564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>199</v>
       </c>
@@ -4583,7 +4587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>201</v>
       </c>
@@ -4606,7 +4610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>203</v>
       </c>
@@ -4629,7 +4633,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>205</v>
       </c>
@@ -4652,7 +4656,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>207</v>
       </c>
@@ -4675,7 +4679,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>209</v>
       </c>
@@ -4698,7 +4702,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>211</v>
       </c>
@@ -4721,7 +4725,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>213</v>
       </c>
@@ -4744,7 +4748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>215</v>
       </c>
@@ -4767,7 +4771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>217</v>
       </c>
@@ -4790,7 +4794,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>219</v>
       </c>
@@ -4813,7 +4817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>221</v>
       </c>
@@ -4836,7 +4840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="2" t="s">
         <v>223</v>
       </c>
@@ -4859,7 +4863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="2" t="s">
         <v>225</v>
       </c>
@@ -4882,7 +4886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="2" t="s">
         <v>227</v>
       </c>
@@ -4905,7 +4909,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="2" t="s">
         <v>229</v>
       </c>
@@ -4928,7 +4932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="2" t="s">
         <v>231</v>
       </c>
@@ -4951,7 +4955,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>233</v>
       </c>
@@ -4974,7 +4978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>235</v>
       </c>
@@ -4997,7 +5001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="1" t="s">
         <v>237</v>
       </c>
@@ -5021,7 +5025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>238</v>
       </c>
@@ -5044,7 +5048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="2" t="s">
         <v>240</v>
       </c>
@@ -5067,7 +5071,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>242</v>
       </c>
@@ -5090,7 +5094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>244</v>
       </c>
@@ -5113,7 +5117,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>246</v>
       </c>
@@ -5136,7 +5140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>248</v>
       </c>
@@ -5159,7 +5163,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>250</v>
       </c>
@@ -5182,7 +5186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="2" t="s">
         <v>252</v>
       </c>
@@ -5205,7 +5209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="2" t="s">
         <v>254</v>
       </c>
@@ -5228,7 +5232,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="2" t="s">
         <v>256</v>
       </c>
@@ -5251,7 +5255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="2" t="s">
         <v>258</v>
       </c>
@@ -5274,7 +5278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="2" t="s">
         <v>260</v>
       </c>
@@ -5297,7 +5301,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="2" t="s">
         <v>262</v>
       </c>
@@ -5320,7 +5324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>264</v>
       </c>
@@ -5343,7 +5347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="2" t="s">
         <v>266</v>
       </c>
@@ -5366,7 +5370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="2" t="s">
         <v>268</v>
       </c>
@@ -5389,7 +5393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="2" t="s">
         <v>270</v>
       </c>
@@ -5412,7 +5416,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="2" t="s">
         <v>272</v>
       </c>
@@ -5435,7 +5439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="2" t="s">
         <v>274</v>
       </c>
@@ -5458,7 +5462,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="2" t="s">
         <v>276</v>
       </c>
@@ -5481,7 +5485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>278</v>
       </c>
@@ -5504,7 +5508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="1" t="s">
         <v>280</v>
       </c>
@@ -5528,7 +5532,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>281</v>
       </c>
@@ -5551,7 +5555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>283</v>
       </c>
@@ -5574,7 +5578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>285</v>
       </c>
@@ -5597,7 +5601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>287</v>
       </c>
@@ -5620,7 +5624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="2" t="s">
         <v>289</v>
       </c>
@@ -5643,7 +5647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="2" t="s">
         <v>291</v>
       </c>
@@ -5666,7 +5670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="2" t="s">
         <v>293</v>
       </c>
@@ -5689,7 +5693,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="2" t="s">
         <v>295</v>
       </c>
@@ -5712,7 +5716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="2" t="s">
         <v>297</v>
       </c>
@@ -5735,7 +5739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="2" t="s">
         <v>299</v>
       </c>
@@ -5758,7 +5762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="2" t="s">
         <v>301</v>
       </c>
@@ -5781,7 +5785,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="2" t="s">
         <v>303</v>
       </c>
@@ -5804,7 +5808,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="2" t="s">
         <v>305</v>
       </c>
@@ -5827,7 +5831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="2" t="s">
         <v>307</v>
       </c>
@@ -5850,7 +5854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="2" t="s">
         <v>309</v>
       </c>
@@ -5873,7 +5877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="2" t="s">
         <v>311</v>
       </c>
@@ -5896,7 +5900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="2" t="s">
         <v>313</v>
       </c>
@@ -5919,7 +5923,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="2" t="s">
         <v>315</v>
       </c>
@@ -5942,7 +5946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="2" t="s">
         <v>317</v>
       </c>
@@ -5965,7 +5969,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="2" t="s">
         <v>319</v>
       </c>
@@ -5988,7 +5992,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="2" t="s">
         <v>321</v>
       </c>
@@ -6011,7 +6015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="2" t="s">
         <v>323</v>
       </c>
@@ -6034,7 +6038,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="2" t="s">
         <v>325</v>
       </c>
@@ -6057,7 +6061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="2" t="s">
         <v>327</v>
       </c>
@@ -6080,7 +6084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="2" t="s">
         <v>329</v>
       </c>
@@ -6103,7 +6107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="2" t="s">
         <v>331</v>
       </c>
@@ -6126,7 +6130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="2" t="s">
         <v>333</v>
       </c>
@@ -6149,7 +6153,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="2" t="s">
         <v>335</v>
       </c>
@@ -6172,7 +6176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="2" t="s">
         <v>337</v>
       </c>
@@ -6195,7 +6199,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="2" t="s">
         <v>339</v>
       </c>
@@ -6218,7 +6222,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="2" t="s">
         <v>341</v>
       </c>
@@ -6241,7 +6245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
         <v>343</v>
       </c>
@@ -6264,7 +6268,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" t="s">
         <v>345</v>
       </c>
@@ -6287,7 +6291,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" t="s">
         <v>347</v>
       </c>
@@ -6310,7 +6314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" t="s">
         <v>349</v>
       </c>
@@ -6333,7 +6337,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
         <v>351</v>
       </c>
@@ -6356,7 +6360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" t="s">
         <v>353</v>
       </c>
@@ -6379,7 +6383,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" t="s">
         <v>355</v>
       </c>
@@ -6402,7 +6406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" t="s">
         <v>357</v>
       </c>
@@ -6425,7 +6429,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" t="s">
         <v>359</v>
       </c>
@@ -6448,7 +6452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" t="s">
         <v>361</v>
       </c>
@@ -6471,7 +6475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="1" t="s">
         <v>363</v>
       </c>
@@ -6495,7 +6499,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" t="s">
         <v>364</v>
       </c>
@@ -6518,7 +6522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" t="s">
         <v>366</v>
       </c>
@@ -6541,7 +6545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" t="s">
         <v>368</v>
       </c>
@@ -6564,7 +6568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" t="s">
         <v>370</v>
       </c>
@@ -6587,7 +6591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" t="s">
         <v>372</v>
       </c>
@@ -6610,7 +6614,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" t="s">
         <v>374</v>
       </c>
@@ -6633,7 +6637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" t="s">
         <v>376</v>
       </c>
@@ -6656,7 +6660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" t="s">
         <v>378</v>
       </c>
@@ -6679,7 +6683,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" t="s">
         <v>380</v>
       </c>
@@ -6702,7 +6706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" t="s">
         <v>382</v>
       </c>
@@ -6725,7 +6729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" t="s">
         <v>384</v>
       </c>
@@ -6748,7 +6752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" t="s">
         <v>386</v>
       </c>
@@ -6771,7 +6775,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" t="s">
         <v>388</v>
       </c>
@@ -6794,7 +6798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" t="s">
         <v>390</v>
       </c>
@@ -6817,7 +6821,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" t="s">
         <v>393</v>
       </c>
@@ -6840,7 +6844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" t="s">
         <v>395</v>
       </c>
@@ -6863,7 +6867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="2" t="s">
         <v>397</v>
       </c>
@@ -6886,7 +6890,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" t="s">
         <v>400</v>
       </c>
@@ -6909,7 +6913,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" t="s">
         <v>402</v>
       </c>
@@ -6932,7 +6936,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" t="s">
         <v>404</v>
       </c>
@@ -6955,7 +6959,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" t="s">
         <v>406</v>
       </c>
@@ -6978,7 +6982,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" t="s">
         <v>408</v>
       </c>
@@ -7001,7 +7005,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="1" t="s">
         <v>410</v>
       </c>
@@ -7025,7 +7029,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="2" t="s">
         <v>411</v>
       </c>
@@ -7048,7 +7052,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="2" t="s">
         <v>411</v>
       </c>
@@ -7071,7 +7075,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" t="s">
         <v>416</v>
       </c>
@@ -7094,7 +7098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="1" t="s">
         <v>418</v>
       </c>
@@ -7118,7 +7122,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" t="s">
         <v>419</v>
       </c>
@@ -7141,7 +7145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" t="s">
         <v>421</v>
       </c>
@@ -7164,7 +7168,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" t="s">
         <v>423</v>
       </c>
@@ -7187,7 +7191,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" t="s">
         <v>425</v>
       </c>
@@ -7210,7 +7214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" t="s">
         <v>427</v>
       </c>
@@ -7233,7 +7237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" t="s">
         <v>429</v>
       </c>
@@ -7256,7 +7260,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" t="s">
         <v>431</v>
       </c>
@@ -7279,7 +7283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" t="s">
         <v>433</v>
       </c>
@@ -7302,7 +7306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" t="s">
         <v>435</v>
       </c>
@@ -7325,7 +7329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="1" t="s">
         <v>437</v>
       </c>
@@ -7349,7 +7353,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" t="s">
         <v>438</v>
       </c>
@@ -7372,7 +7376,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" t="s">
         <v>440</v>
       </c>
@@ -7395,7 +7399,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" t="s">
         <v>442</v>
       </c>
@@ -7418,7 +7422,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" t="s">
         <v>444</v>
       </c>
@@ -7441,7 +7445,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" t="s">
         <v>446</v>
       </c>
@@ -7464,7 +7468,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" t="s">
         <v>448</v>
       </c>
@@ -7487,7 +7491,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" t="s">
         <v>450</v>
       </c>
@@ -7510,7 +7514,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" t="s">
         <v>452</v>
       </c>
@@ -7533,7 +7537,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" t="s">
         <v>454</v>
       </c>
@@ -7556,7 +7560,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" t="s">
         <v>456</v>
       </c>
@@ -7579,7 +7583,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" t="s">
         <v>458</v>
       </c>
@@ -7602,7 +7606,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" t="s">
         <v>460</v>
       </c>
@@ -7625,7 +7629,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="1" t="s">
         <v>462</v>
       </c>
@@ -7649,7 +7653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" t="s">
         <v>463</v>
       </c>
@@ -7672,7 +7676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="2" t="s">
         <v>465</v>
       </c>
@@ -7695,7 +7699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" t="s">
         <v>467</v>
       </c>
@@ -7719,7 +7723,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G235"/>
+  <autoFilter ref="A1:G235">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="PRDD005"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Rega_Local_Idcontador_origem_ZMC.xlsx
+++ b/Rega_Local_Idcontador_origem_ZMC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\regin\Desktop\ShareFiles\QGIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{E66011A2-496E-4671-B95E-08BE99B6E3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A577903-46E0-41F3-9C39-2A63A3D3900A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10272"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="17020" windowHeight="10000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="comb" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">comb!$A$1:$G$235</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="476">
   <si>
     <t>IDLocaliza</t>
   </si>
@@ -1435,9 +1448,6 @@
     <t>Triângulo VG AdA</t>
   </si>
   <si>
-    <t>Furo</t>
-  </si>
-  <si>
     <t>Ada</t>
   </si>
   <si>
@@ -1445,12 +1455,21 @@
   </si>
   <si>
     <t>PE Dunas Douradas Furo 2 e 4 DD</t>
+  </si>
+  <si>
+    <t>chuveiros da praia</t>
+  </si>
+  <si>
+    <t>bomba do lago d.filipa</t>
+  </si>
+  <si>
+    <t>desactivado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2299,20 +2318,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G235"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="16.9453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.89453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.9453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2335,7 +2353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2349,13 +2367,13 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>470</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2375,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2395,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2415,7 +2433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -2438,7 +2456,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -2461,7 +2479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2484,7 +2502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2507,7 +2525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2530,7 +2548,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -2544,7 +2562,7 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
@@ -2553,7 +2571,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -2576,30 +2594,30 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2622,7 +2640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2645,7 +2663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2668,7 +2686,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -2691,7 +2709,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -2714,7 +2732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -2737,7 +2755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -2760,7 +2778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -2783,7 +2801,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -2806,7 +2824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -2829,7 +2847,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -2852,7 +2870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -2875,7 +2893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -2898,7 +2916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
@@ -2922,7 +2940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>64</v>
       </c>
@@ -2946,7 +2964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -2969,7 +2987,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -2992,7 +3010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -3015,7 +3033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -3038,7 +3056,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -3061,7 +3079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -3084,7 +3102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -3107,7 +3125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -3130,7 +3148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -3153,7 +3171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -3176,7 +3194,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -3199,7 +3217,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -3222,7 +3240,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>90</v>
       </c>
@@ -3245,7 +3263,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>92</v>
       </c>
@@ -3268,7 +3286,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -3291,7 +3309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -3314,7 +3332,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -3337,7 +3355,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>100</v>
       </c>
@@ -3355,13 +3373,13 @@
         <v>12</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>12</v>
+        <v>474</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>101</v>
       </c>
@@ -3384,7 +3402,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -3407,7 +3425,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>105</v>
       </c>
@@ -3425,13 +3443,13 @@
         <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -3454,7 +3472,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>108</v>
       </c>
@@ -3472,13 +3490,13 @@
         <v>12</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>12</v>
+        <v>475</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>109</v>
       </c>
@@ -3501,7 +3519,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>111</v>
       </c>
@@ -3524,7 +3542,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>113</v>
       </c>
@@ -3547,7 +3565,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>115</v>
       </c>
@@ -3571,7 +3589,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>116</v>
       </c>
@@ -3595,7 +3613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>117</v>
       </c>
@@ -3619,7 +3637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>118</v>
       </c>
@@ -3643,7 +3661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>119</v>
       </c>
@@ -3666,7 +3684,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>122</v>
       </c>
@@ -3690,7 +3708,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>123</v>
       </c>
@@ -3713,7 +3731,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>125</v>
       </c>
@@ -3736,7 +3754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>127</v>
       </c>
@@ -3759,7 +3777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -3782,7 +3800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>131</v>
       </c>
@@ -3805,7 +3823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>133</v>
       </c>
@@ -3828,7 +3846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>135</v>
       </c>
@@ -3851,7 +3869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>137</v>
       </c>
@@ -3874,7 +3892,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>139</v>
       </c>
@@ -3897,7 +3915,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>141</v>
       </c>
@@ -3920,7 +3938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>143</v>
       </c>
@@ -3943,7 +3961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>145</v>
       </c>
@@ -3966,7 +3984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>147</v>
       </c>
@@ -3989,7 +4007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>149</v>
       </c>
@@ -4012,7 +4030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>151</v>
       </c>
@@ -4035,7 +4053,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>153</v>
       </c>
@@ -4058,7 +4076,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>155</v>
       </c>
@@ -4081,7 +4099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>157</v>
       </c>
@@ -4104,7 +4122,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>159</v>
       </c>
@@ -4127,7 +4145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>161</v>
       </c>
@@ -4150,7 +4168,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>163</v>
       </c>
@@ -4173,7 +4191,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>165</v>
       </c>
@@ -4196,7 +4214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>167</v>
       </c>
@@ -4219,7 +4237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>169</v>
       </c>
@@ -4242,7 +4260,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>171</v>
       </c>
@@ -4265,7 +4283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>173</v>
       </c>
@@ -4288,7 +4306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>175</v>
       </c>
@@ -4311,7 +4329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>177</v>
       </c>
@@ -4334,7 +4352,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>179</v>
       </c>
@@ -4357,7 +4375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>181</v>
       </c>
@@ -4380,7 +4398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>183</v>
       </c>
@@ -4403,7 +4421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>185</v>
       </c>
@@ -4426,7 +4444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>187</v>
       </c>
@@ -4449,7 +4467,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>189</v>
       </c>
@@ -4472,7 +4490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>191</v>
       </c>
@@ -4495,7 +4513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>193</v>
       </c>
@@ -4518,7 +4536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>195</v>
       </c>
@@ -4541,7 +4559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>197</v>
       </c>
@@ -4564,7 +4582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>199</v>
       </c>
@@ -4587,7 +4605,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>201</v>
       </c>
@@ -4610,7 +4628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>203</v>
       </c>
@@ -4633,7 +4651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>205</v>
       </c>
@@ -4656,7 +4674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>207</v>
       </c>
@@ -4679,7 +4697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>209</v>
       </c>
@@ -4702,7 +4720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>211</v>
       </c>
@@ -4725,7 +4743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>213</v>
       </c>
@@ -4748,7 +4766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>215</v>
       </c>
@@ -4771,7 +4789,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>217</v>
       </c>
@@ -4794,7 +4812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>219</v>
       </c>
@@ -4817,7 +4835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>221</v>
       </c>
@@ -4840,7 +4858,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>223</v>
       </c>
@@ -4863,7 +4881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>225</v>
       </c>
@@ -4886,7 +4904,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>227</v>
       </c>
@@ -4909,7 +4927,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>229</v>
       </c>
@@ -4932,7 +4950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>231</v>
       </c>
@@ -4955,7 +4973,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>233</v>
       </c>
@@ -4978,7 +4996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>235</v>
       </c>
@@ -5001,7 +5019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>237</v>
       </c>
@@ -5025,7 +5043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>238</v>
       </c>
@@ -5048,7 +5066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>240</v>
       </c>
@@ -5071,7 +5089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>242</v>
       </c>
@@ -5094,7 +5112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>244</v>
       </c>
@@ -5117,7 +5135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>246</v>
       </c>
@@ -5140,7 +5158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>248</v>
       </c>
@@ -5163,7 +5181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>250</v>
       </c>
@@ -5186,7 +5204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>252</v>
       </c>
@@ -5209,7 +5227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>254</v>
       </c>
@@ -5232,7 +5250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>256</v>
       </c>
@@ -5255,7 +5273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>258</v>
       </c>
@@ -5278,7 +5296,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>260</v>
       </c>
@@ -5301,7 +5319,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>262</v>
       </c>
@@ -5324,7 +5342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>264</v>
       </c>
@@ -5347,7 +5365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>266</v>
       </c>
@@ -5370,7 +5388,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>268</v>
       </c>
@@ -5393,7 +5411,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>270</v>
       </c>
@@ -5416,7 +5434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>272</v>
       </c>
@@ -5439,7 +5457,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>274</v>
       </c>
@@ -5462,7 +5480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>276</v>
       </c>
@@ -5485,7 +5503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>278</v>
       </c>
@@ -5508,7 +5526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>280</v>
       </c>
@@ -5532,7 +5550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>281</v>
       </c>
@@ -5555,7 +5573,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>283</v>
       </c>
@@ -5578,7 +5596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>285</v>
       </c>
@@ -5601,7 +5619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>287</v>
       </c>
@@ -5624,7 +5642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>289</v>
       </c>
@@ -5647,7 +5665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>291</v>
       </c>
@@ -5670,7 +5688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>293</v>
       </c>
@@ -5693,7 +5711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>295</v>
       </c>
@@ -5716,7 +5734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>297</v>
       </c>
@@ -5739,7 +5757,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>299</v>
       </c>
@@ -5762,7 +5780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>301</v>
       </c>
@@ -5785,7 +5803,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>303</v>
       </c>
@@ -5808,7 +5826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>305</v>
       </c>
@@ -5831,7 +5849,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>307</v>
       </c>
@@ -5854,7 +5872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>309</v>
       </c>
@@ -5877,7 +5895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>311</v>
       </c>
@@ -5900,7 +5918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>313</v>
       </c>
@@ -5923,7 +5941,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>315</v>
       </c>
@@ -5946,7 +5964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>317</v>
       </c>
@@ -5969,7 +5987,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>319</v>
       </c>
@@ -5992,7 +6010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>321</v>
       </c>
@@ -6015,7 +6033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>323</v>
       </c>
@@ -6038,7 +6056,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>325</v>
       </c>
@@ -6061,7 +6079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>327</v>
       </c>
@@ -6084,7 +6102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>329</v>
       </c>
@@ -6107,7 +6125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>331</v>
       </c>
@@ -6130,7 +6148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>333</v>
       </c>
@@ -6153,7 +6171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>335</v>
       </c>
@@ -6176,7 +6194,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>337</v>
       </c>
@@ -6199,7 +6217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>339</v>
       </c>
@@ -6222,7 +6240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>341</v>
       </c>
@@ -6245,7 +6263,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>343</v>
       </c>
@@ -6268,7 +6286,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>345</v>
       </c>
@@ -6291,7 +6309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>347</v>
       </c>
@@ -6314,7 +6332,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>349</v>
       </c>
@@ -6337,7 +6355,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>351</v>
       </c>
@@ -6360,7 +6378,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>353</v>
       </c>
@@ -6383,7 +6401,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>355</v>
       </c>
@@ -6406,7 +6424,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>357</v>
       </c>
@@ -6429,7 +6447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>359</v>
       </c>
@@ -6452,7 +6470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>361</v>
       </c>
@@ -6475,7 +6493,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>363</v>
       </c>
@@ -6499,7 +6517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>364</v>
       </c>
@@ -6522,7 +6540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>366</v>
       </c>
@@ -6545,7 +6563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>368</v>
       </c>
@@ -6568,7 +6586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>370</v>
       </c>
@@ -6591,7 +6609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>372</v>
       </c>
@@ -6614,7 +6632,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>374</v>
       </c>
@@ -6637,7 +6655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>376</v>
       </c>
@@ -6660,7 +6678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>378</v>
       </c>
@@ -6683,7 +6701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>380</v>
       </c>
@@ -6706,7 +6724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>382</v>
       </c>
@@ -6729,7 +6747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>384</v>
       </c>
@@ -6752,7 +6770,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>386</v>
       </c>
@@ -6775,7 +6793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>388</v>
       </c>
@@ -6798,7 +6816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>390</v>
       </c>
@@ -6821,7 +6839,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>393</v>
       </c>
@@ -6844,7 +6862,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>395</v>
       </c>
@@ -6867,7 +6885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>397</v>
       </c>
@@ -6890,7 +6908,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>400</v>
       </c>
@@ -6913,7 +6931,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>402</v>
       </c>
@@ -6936,7 +6954,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>404</v>
       </c>
@@ -6959,7 +6977,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>406</v>
       </c>
@@ -6982,7 +7000,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>408</v>
       </c>
@@ -7005,7 +7023,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>410</v>
       </c>
@@ -7029,7 +7047,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>411</v>
       </c>
@@ -7052,7 +7070,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>411</v>
       </c>
@@ -7075,7 +7093,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>416</v>
       </c>
@@ -7098,7 +7116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>418</v>
       </c>
@@ -7122,7 +7140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>419</v>
       </c>
@@ -7145,7 +7163,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>421</v>
       </c>
@@ -7168,7 +7186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>423</v>
       </c>
@@ -7191,7 +7209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>425</v>
       </c>
@@ -7214,7 +7232,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>427</v>
       </c>
@@ -7237,7 +7255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>429</v>
       </c>
@@ -7260,7 +7278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>431</v>
       </c>
@@ -7283,7 +7301,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>433</v>
       </c>
@@ -7306,7 +7324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>435</v>
       </c>
@@ -7329,7 +7347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>437</v>
       </c>
@@ -7353,7 +7371,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>438</v>
       </c>
@@ -7376,7 +7394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>440</v>
       </c>
@@ -7399,7 +7417,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>442</v>
       </c>
@@ -7422,7 +7440,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>444</v>
       </c>
@@ -7445,7 +7463,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>446</v>
       </c>
@@ -7468,7 +7486,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>448</v>
       </c>
@@ -7491,7 +7509,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>450</v>
       </c>
@@ -7514,7 +7532,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>452</v>
       </c>
@@ -7537,7 +7555,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>454</v>
       </c>
@@ -7560,7 +7578,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>456</v>
       </c>
@@ -7583,7 +7601,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>458</v>
       </c>
@@ -7606,7 +7624,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>460</v>
       </c>
@@ -7629,7 +7647,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>462</v>
       </c>
@@ -7653,7 +7671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>463</v>
       </c>
@@ -7676,7 +7694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>465</v>
       </c>
@@ -7699,7 +7717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>467</v>
       </c>
@@ -7723,13 +7741,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G235">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="PRDD005"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G235" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
